--- a/SGC-CKN/Excel/38ff0d4c-be29-4441-8a5e-62aab853e6e8_Lô_CT-02_P1-20_D800_01-04-2026.xlsx
+++ b/SGC-CKN/Excel/38ff0d4c-be29-4441-8a5e-62aab853e6e8_Lô_CT-02_P1-20_D800_01-04-2026.xlsx
@@ -59,7 +59,7 @@
     <t>Kết thúc thi công</t>
   </si>
   <si>
-    <t>17:25 01/04/2026</t>
+    <t>17:25 02/04/2026</t>
   </si>
   <si>
     <t>Địa chất TT</t>
@@ -179,7 +179,7 @@
     <t>Sỏi xám vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
-    <t xml:space="preserve">17:10
+    <t xml:space="preserve">17:25
 01/04/2026</t>
   </si>
   <si>
@@ -303,7 +303,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -368,6 +368,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA5F3FC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
@@ -463,7 +468,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -552,13 +557,16 @@
     <xf numFmtId="0" fontId="12" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1357,16 +1365,16 @@
         <v>-26.5</v>
       </c>
       <c r="G17" s="24">
-        <v>-33.75</v>
+        <v>-38.75</v>
       </c>
       <c r="H17" s="24">
         <v>0.63</v>
       </c>
       <c r="I17" s="24">
-        <v>7.25</v>
+        <v>12.25</v>
       </c>
       <c r="J17" s="8">
-        <v>11.45</v>
+        <v>19.34</v>
       </c>
       <c r="K17" s="25" t="s">
         <v>30</v>
@@ -1389,38 +1397,38 @@
         <v>52</v>
       </c>
       <c r="F18" s="27">
-        <v>-33.75</v>
+        <v>-38.75</v>
       </c>
       <c r="G18" s="27">
-        <v>-44.08</v>
+        <v>-44.48</v>
       </c>
       <c r="H18" s="27">
-        <v>1.62</v>
+        <v>1.87</v>
       </c>
       <c r="I18" s="27">
-        <v>10.33</v>
-      </c>
-      <c r="J18" s="8">
-        <v>6.39</v>
+        <v>5.73</v>
+      </c>
+      <c r="J18" s="30">
+        <v>3.07</v>
       </c>
       <c r="K18" s="28" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="30" t="s">
+      <c r="A21" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="B21" s="30"/>
-      <c r="C21" s="30"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="30"/>
-      <c r="F21" s="30"/>
-      <c r="G21" s="30"/>
-      <c r="H21" s="30"/>
-      <c r="I21" s="30"/>
-      <c r="J21" s="30"/>
-      <c r="K21" s="30"/>
+      <c r="B21" s="31"/>
+      <c r="C21" s="31"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="31"/>
+      <c r="G21" s="31"/>
+      <c r="H21" s="31"/>
+      <c r="I21" s="31"/>
+      <c r="J21" s="31"/>
+      <c r="K21" s="31"/>
     </row>
     <row r="22" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1733,16 +1741,16 @@
         <v>-26.5</v>
       </c>
       <c r="F8" s="24">
-        <v>-33.75</v>
+        <v>-38.75</v>
       </c>
       <c r="G8" s="24">
         <v>0.63</v>
       </c>
       <c r="H8" s="24">
-        <v>7.25</v>
+        <v>12.25</v>
       </c>
       <c r="I8" s="8">
-        <v>11.45</v>
+        <v>19.34</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1759,48 +1767,48 @@
         <v>1</v>
       </c>
       <c r="E9" s="27">
-        <v>-33.75</v>
+        <v>-38.75</v>
       </c>
       <c r="F9" s="27">
-        <v>-44.08</v>
+        <v>-44.48</v>
       </c>
       <c r="G9" s="27">
-        <v>1.62</v>
+        <v>1.87</v>
       </c>
       <c r="H9" s="27">
-        <v>10.33</v>
-      </c>
-      <c r="I9" s="8">
-        <v>6.39</v>
+        <v>5.73</v>
+      </c>
+      <c r="I9" s="30">
+        <v>3.07</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="B10" s="32" t="s">
+      <c r="B10" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="32" t="s">
+      <c r="C10" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="32">
+      <c r="D10" s="33">
         <v>8</v>
       </c>
-      <c r="E10" s="32">
+      <c r="E10" s="33">
         <v>0</v>
       </c>
-      <c r="F10" s="32">
-        <v>-44.08</v>
-      </c>
-      <c r="G10" s="32">
-        <v>4.83</v>
-      </c>
-      <c r="H10" s="32">
-        <v>44.08</v>
-      </c>
-      <c r="I10" s="32">
-        <v>9.12</v>
+      <c r="F10" s="33">
+        <v>-44.48</v>
+      </c>
+      <c r="G10" s="33">
+        <v>5.08</v>
+      </c>
+      <c r="H10" s="33">
+        <v>44.48</v>
+      </c>
+      <c r="I10" s="33">
+        <v>8.75</v>
       </c>
     </row>
   </sheetData>
